--- a/output/graficos_dimensiones/comunal_s_isapre_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2022_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:03</t>
+    <t xml:space="preserve">2026-09-09 22:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_isapre_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2022_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:55</t>
+    <t xml:space="preserve">2026-09-18 10:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_isapre_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2022_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:18</t>
+    <t xml:space="preserve">2026-09-23 12:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_isapre_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2022_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:21</t>
+    <t xml:space="preserve">2026-10-02 14:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_isapre_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2022_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:00</t>
+    <t xml:space="preserve">2026-10-05 09:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
